--- a/data/generated_documents/Manufacturing/Manufacturing_Document_032.xlsx
+++ b/data/generated_documents/Manufacturing/Manufacturing_Document_032.xlsx
@@ -624,7 +624,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-10-21</t>
+          <t>Generated: 2026-10-28</t>
         </is>
       </c>
     </row>
